--- a/soluciones/hojas/Ejercicio3.xlsx
+++ b/soluciones/hojas/Ejercicio3.xlsx
@@ -754,16 +754,16 @@
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">B6-B7-B10*B8*B9</f>
-        <v>0</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="4" t="n">
         <f aca="false">B9</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -772,7 +772,7 @@
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">SQRT(B8^2+B9^2+2*B10*B8*B9)</f>
-        <v>0</v>
+        <v>0.317647603485372</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -781,7 +781,7 @@
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">IF(OR(B15=0,B9=0),"No definida",(B9+B10*B8)/B15)</f>
-        <v>0</v>
+        <v>0.692591405022615</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -790,7 +790,7 @@
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">B2*EXP((B6-B7)*B11)</f>
-        <v>0</v>
+        <v>102.020134002676</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -799,7 +799,7 @@
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">B2*EXP(B13*B11)</f>
-        <v>0</v>
+        <v>99.6007989343992</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -808,7 +808,7 @@
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">B8*SQRT(B11)</f>
-        <v>0</v>
+        <v>0.353553390593274</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -817,7 +817,7 @@
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">IF(B19=0,0,LN(B17/B3)/B19+B19/2)</f>
-        <v>0</v>
+        <v>0.0953458140339195</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -826,7 +826,7 @@
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">B20-B19</f>
-        <v>0</v>
+        <v>-0.258207576559354</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -835,7 +835,7 @@
       </c>
       <c r="B22" s="0" t="n">
         <f aca="false">IF(B19=0,0,LN(B18/B3)/B19+B19/2)</f>
-        <v>0</v>
+        <v>0.0274635630400112</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -844,7 +844,7 @@
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">B22-B19</f>
-        <v>0</v>
+        <v>-0.326089827553263</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -870,7 +870,7 @@
         <v>39</v>
       </c>
       <c r="B26" s="0" t="n">
-        <f aca="false">B4*EXP(-B6*B11)*IF(B19=0,MAX(B17-B3,0),B17*norm.s.dist(B20,TRUE())-B3*norm.s.dist(B21,TRUE()))</f>
+        <f aca="false">B4*EXP(-B6*B11)*IF(B19=0,MAX(B17-B3,0),B17*NORMDIST(B20,0,1,TRUE())-B3*NORMDIST(B21,0,1,TRUE()))</f>
         <v>11.3119970043098</v>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="0" t="n">
-        <f aca="false">B12*EXP(-B5*B11)*IF(B19=0,MAX(B18-B3,0),B18*norm.s.dist(B22,TRUE())-B3*norm.s.dist(B23,TRUE()))</f>
+        <f aca="false">B12*EXP(-B5*B11)*IF(B19=0,MAX(B18-B3,0),B18*NORMDIST(B22,0,1,TRUE())-B3*NORMDIST(B23,0,1,TRUE()))</f>
         <v>11.1248906882463</v>
       </c>
     </row>
@@ -888,7 +888,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="0" t="n">
-        <f aca="false">B4*EXP(-B6*B11)*IF(B19=0,MAX(B3-B17,0),B3*norm.s.dist(-B21,TRUE())-B17*norm.s.dist(-B20,TRUE()))</f>
+        <f aca="false">B4*EXP(-B6*B11)*IF(B19=0,MAX(B3-B17,0),B3*NORMDIST(-B21,0,1,TRUE())-B17*NORMDIST(-B20,0,1,TRUE()))</f>
         <v>13.8887184065963</v>
       </c>
     </row>
@@ -897,7 +897,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="0" t="n">
-        <f aca="false">B12*EXP(-B5*B11)*IF(B19=0,MAX(B3-B18,0),B3*norm.s.dist(-B23,TRUE())-B18*norm.s.dist(-B22,TRUE()))</f>
+        <f aca="false">B12*EXP(-B5*B11)*IF(B19=0,MAX(B3-B18,0),B3*NORMDIST(-B23,0,1,TRUE())-B18*NORMDIST(-B22,0,1,TRUE()))</f>
         <v>16.2096667615195</v>
       </c>
     </row>
